--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487905_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487905_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3164</v>
+        <v>2.4483</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0332</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2831</v>
+        <v>1.6061</v>
       </c>
       <c r="G2" t="n">
         <v>0.7028</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4044</v>
+        <v>0.5364</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4468</v>
+        <v>0.2558</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0424</v>
+        <v>0.2806</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6714</v>
+        <v>1.3271</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7233</v>
+        <v>3.4671</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0519</v>
+        <v>-2.14</v>
       </c>
       <c r="G3" t="n">
         <v>1.3318</v>
@@ -688,13 +688,13 @@
         <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2148</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.6506</v>
       </c>
       <c r="U3" t="n">
-        <v>0.308</v>
+        <v>0.2199</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2914</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4647</v>
+        <v>0.9656</v>
       </c>
       <c r="E4" t="n">
         <v>0.9393</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5255</v>
+        <v>0.0264</v>
       </c>
       <c r="G4" t="n">
         <v>-1.554</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.2897</v>
       </c>
       <c r="T4" t="n">
         <v>-0.3948</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1835</v>
+        <v>0.6844</v>
       </c>
       <c r="V4" t="n">
         <v>1.3975</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4151</v>
+        <v>0.7735</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2557</v>
+        <v>1.2018</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6708</v>
+        <v>-0.4283</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3736</v>
+        <v>-0.7843</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3091</v>
+        <v>-0.9231</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0645</v>
+        <v>0.1388</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9858</v>
+        <v>0.4119</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3498</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.636</v>
+        <v>0.9919</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6122</v>
+        <v>-1.1962</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0407</v>
+        <v>-0.3431</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5715</v>
+        <v>-0.8532</v>
       </c>
       <c r="P5" t="n">
         <v>1.2487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4775</v>
+        <v>-0.3985</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6458</v>
+        <v>-0.3776</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1683</v>
+        <v>-0.0209</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9376</v>
+        <v>0.7076</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0322</v>
+        <v>0.6398</v>
       </c>
       <c r="E6" t="n">
-        <v>0.666</v>
+        <v>0.1686</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6338</v>
+        <v>0.4711</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7843</v>
+        <v>-1.8857</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9231</v>
+        <v>0.313</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1388</v>
+        <v>-2.1986</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4119</v>
+        <v>0.3149</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5800999999999999</v>
+        <v>1.3787</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9919</v>
+        <v>-1.0638</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1962</v>
+        <v>-2.2005</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3431</v>
+        <v>-1.0657</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8532</v>
+        <v>-1.1348</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1398</v>
+        <v>0.2143</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9134</v>
+        <v>-0.1681</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2264</v>
+        <v>0.3824</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3841</v>
+        <v>0.5074</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4772</v>
+        <v>-1.3395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0931</v>
+        <v>1.8469</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5004</v>
+        <v>-0.3736</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2834</v>
+        <v>-0.3091</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.0645</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5697</v>
+        <v>-0.9858</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1447</v>
+        <v>-0.3498</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7144</v>
+        <v>-0.636</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0693</v>
+        <v>0.6122</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1387</v>
+        <v>0.0407</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0694</v>
+        <v>0.5715</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2812</v>
+        <v>0.5698</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1924</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4736</v>
+        <v>0.0078</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8137</v>
+        <v>-0.9376</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9813</v>
+        <v>-0.7076</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4448</v>
+        <v>-0.2837</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0334</v>
+        <v>-0.3318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5886</v>
+        <v>0.048</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8857</v>
+        <v>-0.0348</v>
       </c>
       <c r="H8" t="n">
-        <v>0.313</v>
+        <v>-0.5671</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1986</v>
+        <v>0.5323</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3149</v>
+        <v>0.0878</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3787</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0638</v>
+        <v>0.7446</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2005</v>
+        <v>-0.1225</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0657</v>
+        <v>0.0897</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1348</v>
+        <v>-0.2123</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8703</v>
+        <v>0.0861</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3701</v>
+        <v>-0.4195</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4998</v>
+        <v>0.5056</v>
       </c>
       <c r="V8" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6663</v>
+        <v>-0.4935</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0797</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4133</v>
+        <v>0.2399</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.3105</v>
+        <v>-0.5004</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3648</v>
+        <v>0.2834</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9457</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.5265</v>
+        <v>-0.5697</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8257</v>
+        <v>0.1447</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7007</v>
+        <v>-0.7144</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.784</v>
+        <v>0.0693</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5391</v>
+        <v>0.1387</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2449</v>
+        <v>-0.0694</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7055</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9137</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1686</v>
+        <v>-0.3906</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4874</v>
+        <v>-0.0638</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6812</v>
+        <v>-0.3268</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.23</v>
+        <v>0.8137</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>1.9813</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7417</v>
+        <v>-1.5693</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7604</v>
+        <v>-2.8064</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0187</v>
+        <v>1.2372</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0348</v>
+        <v>-5.3105</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5671</v>
+        <v>-2.3648</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5323</v>
+        <v>-2.9457</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0878</v>
+        <v>-4.5265</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-1.8257</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7446</v>
+        <v>-2.7007</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1225</v>
+        <v>-0.784</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0897</v>
+        <v>-0.5391</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2123</v>
+        <v>-0.2449</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8325</v>
+        <v>2.7055</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>2.9137</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3719</v>
+        <v>1.2656</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8482</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4763</v>
+        <v>0.505</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="11">
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6629</v>
+        <v>4.3152</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7554000000000001</v>
+        <v>1.4079</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9074</v>
+        <v>2.9073</v>
       </c>
       <c r="G11" t="n">
         <v>-8.4087</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2035999999999999</v>
+        <v>-0.2035999999999998</v>
       </c>
       <c r="I11" t="n">
         <v>-8.2051</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9409999999999993</v>
+        <v>0.9409999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>4.186399999999999</v>
+        <v>4.1864</v>
       </c>
       <c r="L11" t="n">
         <v>-3.2454</v>
@@ -1312,19 +1312,19 @@
         <v>15.6089</v>
       </c>
       <c r="S11" t="n">
-        <v>2.390900000000001</v>
+        <v>3.0433</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1527000000000002</v>
+        <v>0.8052000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2381</v>
+        <v>2.238</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7254</v>
+        <v>-0.7253999999999998</v>
       </c>
       <c r="W11" t="n">
-        <v>4.8647</v>
+        <v>4.864699999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-5.5899</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3142</v>
+        <v>1.9682</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0306</v>
+        <v>1.0662</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2836</v>
+        <v>0.9019</v>
       </c>
       <c r="G12" t="n">
         <v>0.8017</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1282</v>
+        <v>0.7821</v>
       </c>
       <c r="T12" t="n">
-        <v>1.034</v>
+        <v>0.0696</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0942</v>
+        <v>0.7125</v>
       </c>
       <c r="V12" t="n">
         <v>3.5061</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5862</v>
+        <v>1.3666</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8768</v>
+        <v>2.3057</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2907</v>
+        <v>-0.9391</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3124</v>
+        <v>3.2049</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3283</v>
+        <v>1.6953</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6407</v>
+        <v>1.5096</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5701</v>
+        <v>4.4135</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7808</v>
+        <v>3.0509</v>
       </c>
       <c r="L13" t="n">
-        <v>5.3508</v>
+        <v>1.3626</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2577</v>
+        <v>-1.2086</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5475</v>
+        <v>-1.3556</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2898</v>
+        <v>0.147</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4974</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7055</v>
+        <v>-1.6649</v>
       </c>
       <c r="R13" t="n">
         <v>0.2081</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6615</v>
+        <v>0.0785</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3849</v>
+        <v>-0.4429</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2767</v>
+        <v>0.5213</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1097</v>
+        <v>-0.4599</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5178</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5666</v>
+        <v>1.344</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7699</v>
+        <v>3.341</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2034</v>
+        <v>-1.9971</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2049</v>
+        <v>3.3124</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6953</v>
+        <v>-2.3283</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5096</v>
+        <v>5.6407</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4135</v>
+        <v>4.5701</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0509</v>
+        <v>-0.7808</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3626</v>
+        <v>5.3508</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2086</v>
+        <v>-1.2577</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3556</v>
+        <v>-1.5475</v>
       </c>
       <c r="O14" t="n">
-        <v>0.147</v>
+        <v>0.2898</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.4568</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.6649</v>
+        <v>-2.7055</v>
       </c>
       <c r="R14" t="n">
         <v>0.2081</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7216</v>
+        <v>0.4193</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9786</v>
+        <v>-0.1509</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2571</v>
+        <v>0.5703</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4599</v>
+        <v>0.1097</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4599</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0367</v>
+        <v>-0.0529</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6071</v>
+        <v>-0.2856</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6438</v>
+        <v>0.2328</v>
       </c>
       <c r="G15" t="n">
         <v>1.4782</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.186</v>
+        <v>0.0964</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4567</v>
+        <v>-0.1352</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6427</v>
+        <v>0.2317</v>
       </c>
       <c r="V15" t="n">
         <v>-1.6275</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.1876</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8509</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2728</v>
+        <v>0.449</v>
       </c>
       <c r="G16" t="n">
         <v>1.2792</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2989</v>
+        <v>-0.9085</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.261</v>
+        <v>-0.0467</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0379</v>
+        <v>-0.8618</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3503</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CHACON CARNERO</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5838</v>
+        <v>-0.5225</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-1.6994</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5838</v>
+        <v>1.1769</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.298</v>
+        <v>0.2949</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0939</v>
+        <v>1.5073</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3919</v>
+        <v>-1.2124</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.4398</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.4287</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.298</v>
+        <v>0.7347</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0939</v>
+        <v>0.5183</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3919</v>
+        <v>0.2164</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2857</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.2191</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2857</v>
+        <v>-0.5395</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3573</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3573</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>J. CHACON CARNERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7178</v>
+        <v>-0.5838</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8066</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0888</v>
+        <v>-0.5838</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2949</v>
+        <v>-0.298</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5073</v>
+        <v>0.0939</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2124</v>
+        <v>-0.3919</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4398</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.989</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4287</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7347</v>
+        <v>-0.298</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5183</v>
+        <v>0.0939</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2164</v>
+        <v>-0.3919</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9538</v>
+        <v>-0.2857</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3262</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6276</v>
+        <v>-0.2857</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3573</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6678</v>
+        <v>-1.2924</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.88</v>
+        <v>-2.2847</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2122</v>
+        <v>0.9923</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1215</v>
+        <v>0.9486</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2365</v>
+        <v>-1.0704</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.885</v>
+        <v>2.019</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2928</v>
+        <v>0.8714</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0576</v>
+        <v>-0.2863</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3504</v>
+        <v>1.1577</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1713</v>
+        <v>0.0772</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.294</v>
+        <v>-0.7841</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4654</v>
+        <v>0.8613</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2081</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.7055</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2421</v>
+        <v>-0.576</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4534</v>
+        <v>-0.6805</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2113</v>
+        <v>0.1045</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5802</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5802</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7797</v>
+        <v>-2.0876</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7133</v>
+        <v>-2.0943</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9336</v>
+        <v>0.0067</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9486</v>
+        <v>-1.1215</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0704</v>
+        <v>-0.2365</v>
       </c>
       <c r="I20" t="n">
-        <v>2.019</v>
+        <v>-0.885</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8714</v>
+        <v>-1.2928</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2863</v>
+        <v>0.0576</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1577</v>
+        <v>-1.3504</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0772</v>
+        <v>0.1713</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7841</v>
+        <v>-0.294</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8613</v>
+        <v>0.4654</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6649</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7055</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0634</v>
+        <v>-0.1778</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1091</v>
+        <v>0.2391</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0457</v>
+        <v>-0.4169</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5802</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>-0.5802</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8395</v>
+        <v>-3.6149</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7269</v>
+        <v>-2.6197</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1126</v>
+        <v>-0.9951</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4918</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2852</v>
+        <v>-1.0606</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9786</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3066</v>
+        <v>-0.1891</v>
       </c>
       <c r="V21" t="n">
         <v>-0.23</v>
@@ -2125,37 +2125,37 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.663</v>
+        <v>-3.6629</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9075</v>
+        <v>-2.9074</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7557</v>
+        <v>-0.7554999999999996</v>
       </c>
       <c r="G22" t="n">
         <v>8.408600000000002</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2035</v>
+        <v>0.2035000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>8.205100000000002</v>
       </c>
       <c r="J22" t="n">
-        <v>9.349599999999999</v>
+        <v>9.349600000000001</v>
       </c>
       <c r="K22" t="n">
         <v>4.3899</v>
       </c>
       <c r="L22" t="n">
-        <v>4.9597</v>
+        <v>4.959699999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9410000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.1862</v>
+        <v>-4.186199999999999</v>
       </c>
       <c r="O22" t="n">
         <v>3.2454</v>
@@ -2170,16 +2170,16 @@
         <v>5.202999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3908</v>
+        <v>-2.3909</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.2379</v>
+        <v>-2.2381</v>
       </c>
       <c r="U22" t="n">
         <v>-0.1526999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7252000000000004</v>
+        <v>0.7251999999999996</v>
       </c>
       <c r="W22" t="n">
         <v>5.59</v>
